--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.160.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.160.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0160.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0160.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Every Subp Ã¦ na,</t>
+          <t>L81: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L5: symbol-only separator/garbage line :: 5 0</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L7: isolated marker/symbol line :: t</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,14 +662,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L135: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +677,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L17: symbol-only separator/garbage line :: .50</t>
+          <t>L7: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -728,7 +728,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: 10</t>
+          <t>L17: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -754,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L21: symbol-only separator/garbage line :: .5 0</t>
+          <t>L19: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L22: isolated marker/symbol line :: 50</t>
+          <t>L21: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L24: symbol-only separator/garbage line :: - 0 0</t>
+          <t>L22: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -932,7 +932,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L24: symbol-only separator/garbage line :: - 0 0</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 10</t>
+          <t>L26: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: F,</t>
+          <t>L83: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L87: symbol-only separator/garbage line :: 10 0</t>
+          <t>L85: isolated marker/symbol line :: F,</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L91: symbol-only separator/garbage line :: &gt; 10 0</t>
+          <t>L87: symbol-only separator/garbage line :: 10 0</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L93: symbol-only separator/garbage line :: 25 0</t>
+          <t>L91: symbol-only separator/garbage line :: &gt; 10 0</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: r</t>
+          <t>L93: symbol-only separator/garbage line :: 25 0</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L96: symbol-only separator/garbage line :: )42 0</t>
+          <t>L95: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 10</t>
+          <t>L96: symbol-only separator/garbage line :: )42 0</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: e</t>
+          <t>L98: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 13</t>
+          <t>L100: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L106: symbol-only separator/garbage line :: ,10</t>
+          <t>L105: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L107: symbol-only separator/garbage line :: .10</t>
+          <t>L106: symbol-only separator/garbage line :: ,10</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: r</t>
+          <t>L107: symbol-only separator/garbage line :: .10</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L111: symbol-only separator/garbage line :: .5 0</t>
+          <t>L108: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L113: symbol-only separator/garbage line :: 5 0</t>
+          <t>L111: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: A</t>
+          <t>L113: symbol-only separator/garbage line :: 5 0</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 10</t>
+          <t>L115: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L118: symbol-only separator/garbage line :: .10</t>
+          <t>L117: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L120: symbol-only separator/garbage line :: 0 6</t>
+          <t>L118: symbol-only separator/garbage line :: .10</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L121: symbol-only separator/garbage line :: .5 0</t>
+          <t>L120: symbol-only separator/garbage line :: 0 6</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L123: symbol-only separator/garbage line :: 5 0</t>
+          <t>L121: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L125: symbol-only separator/garbage line :: .2 6</t>
+          <t>L123: symbol-only separator/garbage line :: 5 0</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 04</t>
+          <t>L125: symbol-only separator/garbage line :: .2 6</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L129: symbol-only separator/garbage line :: .50</t>
+          <t>L127: isolated marker/symbol line :: 04</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L131: symbol-only separator/garbage line :: 1 3</t>
+          <t>L129: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: L</t>
+          <t>L131: symbol-only separator/garbage line :: 1 3</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L133: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2018,7 +2018,11 @@
           <t>L57: isolated marker/symbol line :: 0</t>
         </is>
       </c>
-      <c r="O36" s="1" t="inlineStr"/>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L135: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2387,7 +2391,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L81: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
